--- a/assets/schedule.xlsx
+++ b/assets/schedule.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sven/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sven/Develop/Sonstiges/nextjs/nordstern-app/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A8A579F-3E18-774F-9C4A-DB3BC1E09FF1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A6FDDD8-CAFC-9044-A5E8-465864631659}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5480" yWindow="3600" windowWidth="27840" windowHeight="16740" xr2:uid="{CC5531EC-EA4B-4C49-901F-B97AF59B9A20}"/>
   </bookViews>
@@ -523,7 +523,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="5">
-        <v>44646.833333333336</v>
+        <v>44667.791666666664</v>
       </c>
       <c r="H4" s="1"/>
     </row>
@@ -543,6 +543,12 @@
       <c r="E5" s="5">
         <v>44645.833333333336</v>
       </c>
+      <c r="F5" s="7">
+        <v>13</v>
+      </c>
+      <c r="G5" s="7">
+        <v>7</v>
+      </c>
       <c r="H5" s="1"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -561,6 +567,12 @@
       <c r="E6" s="5">
         <v>44646.666666666664</v>
       </c>
+      <c r="F6" s="7">
+        <v>11</v>
+      </c>
+      <c r="G6" s="7">
+        <v>10</v>
+      </c>
       <c r="H6" s="1"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -579,6 +591,12 @@
       <c r="E7" s="5">
         <v>44653.791666666664</v>
       </c>
+      <c r="F7" s="7">
+        <v>12</v>
+      </c>
+      <c r="G7" s="7">
+        <v>8</v>
+      </c>
       <c r="H7" s="1"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -597,6 +615,12 @@
       <c r="E8" s="5">
         <v>44653.770833333336</v>
       </c>
+      <c r="F8" s="7">
+        <v>15</v>
+      </c>
+      <c r="G8" s="7">
+        <v>5</v>
+      </c>
       <c r="H8" s="1"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -614,6 +638,12 @@
       </c>
       <c r="E9" s="5">
         <v>44652.833333333336</v>
+      </c>
+      <c r="F9" s="7">
+        <v>15</v>
+      </c>
+      <c r="G9" s="7">
+        <v>5</v>
       </c>
       <c r="H9" s="1"/>
     </row>
@@ -678,6 +708,12 @@
       </c>
       <c r="E12" s="5">
         <v>44660.833333333336</v>
+      </c>
+      <c r="F12" s="7">
+        <v>7</v>
+      </c>
+      <c r="G12" s="7">
+        <v>13</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>

--- a/assets/schedule.xlsx
+++ b/assets/schedule.xlsx
@@ -1,24 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10212"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sven/Develop/Sonstiges/nextjs/nordstern-app/assets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nowitzky/Development/Private/nordsternApp/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A6FDDD8-CAFC-9044-A5E8-465864631659}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B8D79EC-0324-0B4F-9D58-AA23E3F477D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5480" yWindow="3600" windowWidth="27840" windowHeight="16740" xr2:uid="{CC5531EC-EA4B-4C49-901F-B97AF59B9A20}"/>
+    <workbookView xWindow="16220" yWindow="5300" windowWidth="27840" windowHeight="16740" xr2:uid="{CC5531EC-EA4B-4C49-901F-B97AF59B9A20}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -27,25 +38,25 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="7">
   <si>
-    <t>1. Sythener Dart Club III/99</t>
-  </si>
-  <si>
-    <t>Pub Okay</t>
-  </si>
-  <si>
     <t>DC It's Fun</t>
   </si>
   <si>
     <t>Team Nordstern</t>
   </si>
   <si>
-    <t>Leo´s</t>
+    <t>DC Kneipenterroristen</t>
   </si>
   <si>
-    <t>DC Mythos Görsmeier</t>
+    <t>Dart Freunde Habinghorst</t>
   </si>
   <si>
-    <t>DC Kneipenterroristen</t>
+    <t>1.DC Enterprice</t>
+  </si>
+  <si>
+    <t>DC Balkan</t>
+  </si>
+  <si>
+    <t>German Darts Society</t>
   </si>
 </sst>
 </file>
@@ -55,7 +66,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m\/d\/yyyy\ hh:mm"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -70,11 +81,22 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -97,25 +119,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -435,233 +458,184 @@
   <cols>
     <col min="3" max="3" width="23.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="10.83203125" style="7"/>
+    <col min="5" max="5" width="18.6640625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1">
-        <v>1</v>
-      </c>
-      <c r="B1">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="A1" s="4">
+        <v>1</v>
+      </c>
+      <c r="B1" s="4">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="2">
-        <v>44632.770833333336</v>
-      </c>
-      <c r="F1" s="7">
-        <v>11</v>
-      </c>
-      <c r="G1" s="7">
+      <c r="E1" s="5">
+        <v>44989.791666666664</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4">
+        <v>2</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="5">
+        <v>44989.770833333336</v>
+      </c>
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A3" s="4">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4">
+        <v>3</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="5">
+        <v>44989.8125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A4" s="4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4">
+        <v>4</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="5">
+        <v>44996.770833333336</v>
+      </c>
+      <c r="H4" s="1"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A5" s="4">
+        <v>2</v>
+      </c>
+      <c r="B5" s="4">
+        <v>5</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="6">
+        <v>44995.833333333336</v>
+      </c>
+      <c r="H5" s="1"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A6" s="4">
+        <v>2</v>
+      </c>
+      <c r="B6" s="4">
+        <v>6</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="6">
+        <v>44995.833333333336</v>
+      </c>
+      <c r="H6" s="1"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A7" s="4">
+        <v>3</v>
+      </c>
+      <c r="B7" s="4">
+        <v>7</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E7" s="7">
+        <v>45010.8125</v>
+      </c>
+      <c r="H7" s="1"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A8" s="4">
+        <v>3</v>
+      </c>
+      <c r="B8" s="4">
+        <v>8</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="7">
+        <v>45010.791666666664</v>
+      </c>
+      <c r="H8" s="1"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A9" s="4">
+        <v>3</v>
+      </c>
+      <c r="B9" s="4">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="3">
-        <v>44638.833333333336</v>
-      </c>
-      <c r="F2" s="7">
-        <v>8</v>
-      </c>
-      <c r="G2" s="7">
-        <v>12</v>
-      </c>
-      <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="C3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="4">
-        <v>44632.791666666664</v>
-      </c>
-      <c r="F3" s="7">
-        <v>17</v>
-      </c>
-      <c r="G3" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4">
-        <v>4</v>
-      </c>
-      <c r="C4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="C9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="7">
+        <v>45010.770833333336</v>
+      </c>
+      <c r="H9" s="1"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A10" s="4">
+        <v>4</v>
+      </c>
+      <c r="B10" s="4">
+        <v>10</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="5">
-        <v>44667.791666666664</v>
-      </c>
-      <c r="H4" s="1"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
-        <v>2</v>
-      </c>
-      <c r="E5" s="5">
-        <v>44645.833333333336</v>
-      </c>
-      <c r="F5" s="7">
-        <v>13</v>
-      </c>
-      <c r="G5" s="7">
-        <v>7</v>
-      </c>
-      <c r="H5" s="1"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>2</v>
-      </c>
-      <c r="B6">
-        <v>6</v>
-      </c>
-      <c r="C6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="5">
-        <v>44646.666666666664</v>
-      </c>
-      <c r="F6" s="7">
-        <v>11</v>
-      </c>
-      <c r="G6" s="7">
-        <v>10</v>
-      </c>
-      <c r="H6" s="1"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>3</v>
-      </c>
-      <c r="B7">
-        <v>7</v>
-      </c>
-      <c r="C7" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="5">
-        <v>44653.791666666664</v>
-      </c>
-      <c r="F7" s="7">
-        <v>12</v>
-      </c>
-      <c r="G7" s="7">
-        <v>8</v>
-      </c>
-      <c r="H7" s="1"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>3</v>
-      </c>
-      <c r="B8">
-        <v>8</v>
-      </c>
-      <c r="C8" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="5">
-        <v>44653.770833333336</v>
-      </c>
-      <c r="F8" s="7">
-        <v>15</v>
-      </c>
-      <c r="G8" s="7">
-        <v>5</v>
-      </c>
-      <c r="H8" s="1"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>3</v>
-      </c>
-      <c r="B9">
-        <v>9</v>
-      </c>
-      <c r="C9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="5">
-        <v>44652.833333333336</v>
-      </c>
-      <c r="F9" s="7">
-        <v>15</v>
-      </c>
-      <c r="G9" s="7">
-        <v>5</v>
-      </c>
-      <c r="H9" s="1"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>4</v>
-      </c>
-      <c r="B10">
-        <v>10</v>
-      </c>
-      <c r="C10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" t="s">
-        <v>1</v>
-      </c>
-      <c r="E10" s="5">
-        <v>44660.8125</v>
+      <c r="E10" s="7">
+        <v>45030.833333333336</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -671,20 +645,20 @@
       <c r="N10" s="1"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>4</v>
-      </c>
-      <c r="B11">
+      <c r="A11" s="4">
+        <v>4</v>
+      </c>
+      <c r="B11" s="4">
         <v>11</v>
       </c>
-      <c r="C11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" t="s">
-        <v>2</v>
-      </c>
-      <c r="E11" s="5">
-        <v>44660.666666666664</v>
+      <c r="C11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="7">
+        <v>45030.833333333336</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -694,26 +668,20 @@
       <c r="N11" s="1"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>4</v>
-      </c>
-      <c r="B12">
+      <c r="A12" s="4">
+        <v>4</v>
+      </c>
+      <c r="B12" s="4">
         <v>12</v>
       </c>
-      <c r="C12" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="5">
-        <v>44660.833333333336</v>
-      </c>
-      <c r="F12" s="7">
-        <v>7</v>
-      </c>
-      <c r="G12" s="7">
-        <v>13</v>
+      <c r="C12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E12" s="7">
+        <v>45031.770833333336</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -723,20 +691,20 @@
       <c r="N12" s="1"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>5</v>
-      </c>
-      <c r="B13">
+      <c r="A13" s="4">
+        <v>5</v>
+      </c>
+      <c r="B13" s="4">
         <v>13</v>
       </c>
-      <c r="C13" t="s">
-        <v>1</v>
-      </c>
-      <c r="D13" t="s">
-        <v>3</v>
-      </c>
-      <c r="E13" s="5">
-        <v>44673.833333333336</v>
+      <c r="C13" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E13" s="7">
+        <v>45037.833333333336</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -746,20 +714,20 @@
       <c r="N13" s="1"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>5</v>
-      </c>
-      <c r="B14">
+      <c r="A14" s="4">
+        <v>5</v>
+      </c>
+      <c r="B14" s="4">
         <v>14</v>
       </c>
-      <c r="C14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D14" t="s">
-        <v>6</v>
-      </c>
-      <c r="E14" s="5">
-        <v>44674.791666666664</v>
+      <c r="C14" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" s="7">
+        <v>45038.8125</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -769,20 +737,20 @@
       <c r="N14" s="1"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>5</v>
-      </c>
-      <c r="B15">
+      <c r="A15" s="4">
+        <v>5</v>
+      </c>
+      <c r="B15" s="4">
         <v>15</v>
       </c>
-      <c r="C15" t="s">
-        <v>2</v>
-      </c>
-      <c r="D15" t="s">
-        <v>0</v>
-      </c>
-      <c r="E15" s="5">
-        <v>44673.833333333336</v>
+      <c r="C15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="7">
+        <v>45038.770833333336</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -792,20 +760,20 @@
       <c r="N15" s="1"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>6</v>
-      </c>
-      <c r="B16">
+      <c r="A16" s="4">
+        <v>6</v>
+      </c>
+      <c r="B16" s="4">
         <v>16</v>
       </c>
-      <c r="C16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D16" t="s">
-        <v>1</v>
-      </c>
-      <c r="E16" s="5">
-        <v>44681.666666666664</v>
+      <c r="C16" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E16" s="7">
+        <v>45044.833333333336</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -815,20 +783,20 @@
       <c r="N16" s="1"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>6</v>
-      </c>
-      <c r="B17">
+      <c r="A17" s="4">
+        <v>6</v>
+      </c>
+      <c r="B17" s="4">
         <v>17</v>
       </c>
-      <c r="C17" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E17" s="5">
-        <v>44681.833333333336</v>
+      <c r="C17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E17" s="7">
+        <v>45045.770833333336</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -838,20 +806,20 @@
       <c r="N17" s="1"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>6</v>
-      </c>
-      <c r="B18">
+      <c r="A18" s="4">
+        <v>6</v>
+      </c>
+      <c r="B18" s="4">
         <v>18</v>
       </c>
-      <c r="C18" t="s">
-        <v>0</v>
-      </c>
-      <c r="D18" t="s">
-        <v>4</v>
-      </c>
-      <c r="E18" s="5">
-        <v>44681.770833333336</v>
+      <c r="C18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E18" s="7">
+        <v>45045.8125</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -861,20 +829,20 @@
       <c r="N18" s="1"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A19">
+      <c r="A19" s="4">
         <v>7</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="4">
         <v>19</v>
       </c>
-      <c r="C19" t="s">
-        <v>5</v>
-      </c>
-      <c r="D19" t="s">
-        <v>3</v>
-      </c>
-      <c r="E19" s="5">
-        <v>44695.666666666664</v>
+      <c r="C19" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E19" s="7">
+        <v>45058.833333333336</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -884,20 +852,20 @@
       <c r="N19" s="1"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A20">
+      <c r="A20" s="4">
         <v>7</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="4">
         <v>20</v>
       </c>
-      <c r="C20" t="s">
-        <v>2</v>
-      </c>
-      <c r="D20" t="s">
-        <v>4</v>
-      </c>
-      <c r="E20" s="5">
-        <v>44694.833333333336</v>
+      <c r="C20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E20" s="7">
+        <v>45059.770833333336</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -907,20 +875,20 @@
       <c r="N20" s="1"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A21">
+      <c r="A21" s="4">
         <v>7</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="4">
         <v>21</v>
       </c>
-      <c r="C21" t="s">
-        <v>6</v>
-      </c>
-      <c r="D21" t="s">
-        <v>0</v>
-      </c>
-      <c r="E21" s="5">
-        <v>44695.8125</v>
+      <c r="C21" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E21" s="7">
+        <v>45058.833333333336</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -930,20 +898,20 @@
       <c r="N21" s="1"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A22">
+      <c r="A22" s="4">
         <v>8</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="4">
         <v>22</v>
       </c>
-      <c r="C22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="C22" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E22" s="5">
-        <v>44701.833333333336</v>
+      <c r="D22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22" s="8">
+        <v>45065.833333333336</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -953,20 +921,20 @@
       <c r="N22" s="1"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A23">
+      <c r="A23" s="4">
         <v>8</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="4">
         <v>23</v>
       </c>
-      <c r="C23" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" t="s">
-        <v>2</v>
-      </c>
-      <c r="E23" s="5">
-        <v>44702.833333333336</v>
+      <c r="C23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E23" s="8">
+        <v>45066.770833333336</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -976,20 +944,20 @@
       <c r="N23" s="1"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A24">
+      <c r="A24" s="4">
         <v>8</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="4">
         <v>24</v>
       </c>
-      <c r="C24" t="s">
-        <v>5</v>
-      </c>
-      <c r="D24" t="s">
-        <v>4</v>
-      </c>
-      <c r="E24" s="5">
-        <v>44702.666666666664</v>
+      <c r="C24" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E24" s="8">
+        <v>45065.833333333336</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
@@ -999,20 +967,20 @@
       <c r="N24" s="1"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A25">
+      <c r="A25" s="4">
         <v>9</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="4">
         <v>25</v>
       </c>
-      <c r="C25" t="s">
-        <v>0</v>
-      </c>
-      <c r="D25" t="s">
-        <v>3</v>
-      </c>
-      <c r="E25" s="5">
-        <v>44709.770833333336</v>
+      <c r="C25" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E25" s="8">
+        <v>45073.791666666664</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
@@ -1022,20 +990,20 @@
       <c r="N25" s="1"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A26">
+      <c r="A26" s="4">
         <v>9</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="4">
         <v>26</v>
       </c>
-      <c r="C26" t="s">
-        <v>2</v>
-      </c>
-      <c r="D26" t="s">
-        <v>1</v>
-      </c>
-      <c r="E26" s="5">
-        <v>44708.833333333336</v>
+      <c r="C26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E26" s="8">
+        <v>45073.770833333336</v>
       </c>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
@@ -1045,20 +1013,20 @@
       <c r="N26" s="1"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A27">
+      <c r="A27" s="4">
         <v>9</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="4">
         <v>27</v>
       </c>
-      <c r="C27" t="s">
-        <v>6</v>
-      </c>
-      <c r="D27" t="s">
-        <v>5</v>
-      </c>
-      <c r="E27" s="5">
-        <v>44709.8125</v>
+      <c r="C27" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E27" s="8">
+        <v>45072.833333333336</v>
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
@@ -1068,20 +1036,20 @@
       <c r="N27" s="1"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A28">
+      <c r="A28" s="4">
         <v>10</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="4">
         <v>28</v>
       </c>
-      <c r="C28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D28" t="s">
-        <v>4</v>
-      </c>
-      <c r="E28" s="5">
-        <v>44722.833333333336</v>
+      <c r="C28" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E28" s="8">
+        <v>45086.833333333336</v>
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
@@ -1092,20 +1060,20 @@
       <c r="N28" s="1"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A29">
+      <c r="A29" s="4">
         <v>10</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="4">
         <v>29</v>
       </c>
-      <c r="C29" t="s">
-        <v>5</v>
-      </c>
-      <c r="D29" t="s">
-        <v>0</v>
-      </c>
-      <c r="E29" s="5">
-        <v>44723.666666666664</v>
+      <c r="C29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E29" s="8">
+        <v>45086.833333333336</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
@@ -1116,20 +1084,20 @@
       <c r="N29" s="1"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A30">
+      <c r="A30" s="4">
         <v>10</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="4">
         <v>30</v>
       </c>
-      <c r="C30" t="s">
-        <v>6</v>
-      </c>
-      <c r="D30" t="s">
-        <v>2</v>
-      </c>
-      <c r="E30" s="5">
-        <v>44723.8125</v>
+      <c r="C30" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E30" s="8">
+        <v>45086.833333333336</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
@@ -1140,20 +1108,20 @@
       <c r="N30" s="1"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A31">
+      <c r="A31" s="4">
         <v>11</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="4">
         <v>31</v>
       </c>
-      <c r="C31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D31" t="s">
-        <v>6</v>
-      </c>
-      <c r="E31" s="5">
-        <v>44729.833333333336</v>
+      <c r="C31" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E31" s="8">
+        <v>45093.833333333336</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -1163,20 +1131,20 @@
       <c r="N31" s="1"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A32">
+      <c r="A32" s="4">
         <v>11</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="4">
         <v>32</v>
       </c>
-      <c r="C32" t="s">
-        <v>2</v>
-      </c>
-      <c r="D32" t="s">
-        <v>5</v>
-      </c>
-      <c r="E32" s="5">
-        <v>44729.833333333336</v>
+      <c r="C32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E32" s="8">
+        <v>45094.770833333336</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -1186,20 +1154,20 @@
       <c r="N32" s="1"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A33">
+      <c r="A33" s="4">
         <v>11</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="4">
         <v>33</v>
       </c>
-      <c r="C33" t="s">
-        <v>4</v>
-      </c>
-      <c r="D33" t="s">
-        <v>3</v>
-      </c>
-      <c r="E33" s="5">
-        <v>44730.791666666664</v>
+      <c r="C33" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E33" s="8">
+        <v>45094.8125</v>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -1209,20 +1177,20 @@
       <c r="N33" s="1"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A34">
+      <c r="A34" s="4">
         <v>12</v>
       </c>
-      <c r="B34">
+      <c r="B34" s="4">
         <v>34</v>
       </c>
-      <c r="C34" t="s">
-        <v>3</v>
-      </c>
-      <c r="D34" t="s">
-        <v>1</v>
-      </c>
-      <c r="E34" s="5">
-        <v>44737.833333333336</v>
+      <c r="C34" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E34" s="8">
+        <v>45101.770833333336</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -1232,20 +1200,20 @@
       <c r="N34" s="1"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A35">
+      <c r="A35" s="4">
         <v>12</v>
       </c>
-      <c r="B35">
+      <c r="B35" s="4">
         <v>35</v>
       </c>
-      <c r="C35" t="s">
-        <v>6</v>
-      </c>
-      <c r="D35" t="s">
-        <v>4</v>
-      </c>
-      <c r="E35" s="5">
-        <v>44737.8125</v>
+      <c r="C35" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E35" s="8">
+        <v>45100.833333333336</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
@@ -1255,20 +1223,20 @@
       <c r="N35" s="1"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A36">
+      <c r="A36" s="4">
         <v>12</v>
       </c>
-      <c r="B36">
+      <c r="B36" s="4">
         <v>36</v>
       </c>
-      <c r="C36" t="s">
-        <v>0</v>
-      </c>
-      <c r="D36" t="s">
-        <v>2</v>
-      </c>
-      <c r="E36" s="5">
-        <v>44737.770833333336</v>
+      <c r="C36" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E36" s="8">
+        <v>45101.791666666664</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -1278,20 +1246,20 @@
       <c r="N36" s="1"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A37">
+      <c r="A37" s="4">
         <v>13</v>
       </c>
-      <c r="B37">
+      <c r="B37" s="4">
         <v>37</v>
       </c>
-      <c r="C37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D37" t="s">
-        <v>5</v>
-      </c>
-      <c r="E37" s="5">
-        <v>44750.833333333336</v>
+      <c r="C37" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E37" s="8">
+        <v>45114.833333333336</v>
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
@@ -1301,20 +1269,20 @@
       <c r="N37" s="1"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A38">
+      <c r="A38" s="4">
         <v>13</v>
       </c>
-      <c r="B38">
+      <c r="B38" s="4">
         <v>38</v>
       </c>
-      <c r="C38" t="s">
-        <v>6</v>
-      </c>
-      <c r="D38" t="s">
-        <v>3</v>
-      </c>
-      <c r="E38" s="5">
-        <v>44751.8125</v>
+      <c r="C38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E38" s="8">
+        <v>45114.833333333336</v>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
@@ -1324,20 +1292,20 @@
       <c r="N38" s="1"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A39">
+      <c r="A39" s="4">
         <v>13</v>
       </c>
-      <c r="B39">
+      <c r="B39" s="4">
         <v>39</v>
       </c>
-      <c r="C39" t="s">
-        <v>4</v>
-      </c>
-      <c r="D39" t="s">
-        <v>0</v>
-      </c>
-      <c r="E39" s="5">
-        <v>44751.791666666664</v>
+      <c r="C39" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E39" s="8">
+        <v>45115.8125</v>
       </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
@@ -1347,20 +1315,20 @@
       <c r="N39" s="1"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A40">
+      <c r="A40" s="4">
         <v>14</v>
       </c>
-      <c r="B40">
+      <c r="B40" s="4">
         <v>40</v>
       </c>
-      <c r="C40" t="s">
-        <v>3</v>
-      </c>
-      <c r="D40" t="s">
-        <v>5</v>
-      </c>
-      <c r="E40" s="5">
-        <v>44758.833333333336</v>
+      <c r="C40" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E40" s="8">
+        <v>45122.770833333336</v>
       </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
@@ -1370,20 +1338,20 @@
       <c r="N40" s="1"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A41">
+      <c r="A41" s="4">
         <v>14</v>
       </c>
-      <c r="B41">
+      <c r="B41" s="4">
         <v>41</v>
       </c>
-      <c r="C41" t="s">
-        <v>4</v>
-      </c>
-      <c r="D41" t="s">
-        <v>2</v>
-      </c>
-      <c r="E41" s="5">
-        <v>44758.791666666664</v>
+      <c r="C41" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E41" s="8">
+        <v>45122.8125</v>
       </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
@@ -1393,20 +1361,20 @@
       <c r="N41" s="1"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A42">
+      <c r="A42" s="4">
         <v>14</v>
       </c>
-      <c r="B42">
+      <c r="B42" s="4">
         <v>42</v>
       </c>
-      <c r="C42" t="s">
-        <v>0</v>
-      </c>
-      <c r="D42" t="s">
-        <v>6</v>
-      </c>
-      <c r="E42" s="5">
-        <v>44758.770833333336</v>
+      <c r="C42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E42" s="8">
+        <v>45122.791666666664</v>
       </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>

--- a/assets/schedule.xlsx
+++ b/assets/schedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10212"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10211"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nowitzky/Development/Private/nordsternApp/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B8D79EC-0324-0B4F-9D58-AA23E3F477D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2D97E4A-17CD-364C-B0B3-41AC9413372B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16220" yWindow="5300" windowWidth="27840" windowHeight="16740" xr2:uid="{CC5531EC-EA4B-4C49-901F-B97AF59B9A20}"/>
+    <workbookView xWindow="4900" yWindow="2480" windowWidth="27840" windowHeight="16740" xr2:uid="{CC5531EC-EA4B-4C49-901F-B97AF59B9A20}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,37 +36,115 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="7">
-  <si>
-    <t>DC It's Fun</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="34">
   <si>
     <t>Team Nordstern</t>
   </si>
   <si>
-    <t>DC Kneipenterroristen</t>
-  </si>
-  <si>
-    <t>Dart Freunde Habinghorst</t>
-  </si>
-  <si>
-    <t>1.DC Enterprice</t>
-  </si>
-  <si>
     <t>DC Balkan</t>
   </si>
   <si>
-    <t>German Darts Society</t>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>DC Wanne Eickel 4</t>
+  </si>
+  <si>
+    <t>Die GEstörten</t>
+  </si>
+  <si>
+    <t>20:00</t>
+  </si>
+  <si>
+    <t>Schalker Dartfreunde 94</t>
+  </si>
+  <si>
+    <t>Pub Okay</t>
+  </si>
+  <si>
+    <t>Die die keiner wollte</t>
+  </si>
+  <si>
+    <t>19:00</t>
+  </si>
+  <si>
+    <t>1. Zweckler Dartverein 4</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>04.05.2024</t>
+  </si>
+  <si>
+    <t>03.05.2024</t>
+  </si>
+  <si>
+    <t>20.04.2024</t>
+  </si>
+  <si>
+    <t>12.04.2024</t>
+  </si>
+  <si>
+    <t>13.04.2024</t>
+  </si>
+  <si>
+    <t>23.03.2024</t>
+  </si>
+  <si>
+    <t>15.03.2024</t>
+  </si>
+  <si>
+    <t>16.03.2024</t>
+  </si>
+  <si>
+    <t>02.03.2024</t>
+  </si>
+  <si>
+    <t>24.02.2024</t>
+  </si>
+  <si>
+    <t>23.02.2024</t>
+  </si>
+  <si>
+    <t>11.05.2024</t>
+  </si>
+  <si>
+    <t>18.05.2024</t>
+  </si>
+  <si>
+    <t>17.05.2024</t>
+  </si>
+  <si>
+    <t>01.06.2024</t>
+  </si>
+  <si>
+    <t>08.06.2024</t>
+  </si>
+  <si>
+    <t>07.06.2024</t>
+  </si>
+  <si>
+    <t>22.06.2024</t>
+  </si>
+  <si>
+    <t>29.06.2024</t>
+  </si>
+  <si>
+    <t>28.06.2024</t>
+  </si>
+  <si>
+    <t>13.07.2024</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="m\/d\/yyyy\ hh:mm"/>
-  </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -81,20 +159,7 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
+      <sz val="8"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -119,25 +184,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -453,189 +507,220 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54059753-ED7E-7645-AA85-ACC322BBE23D}">
-  <dimension ref="A1:N42"/>
+  <dimension ref="A1:N56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="23.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1" s="4">
+      <c r="A1" s="2">
         <v>1</v>
       </c>
-      <c r="B1" s="4">
+      <c r="B1" s="2">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2">
         <v>4</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="C4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" s="1"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>2</v>
+      </c>
+      <c r="B5" s="2">
+        <v>5</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="1"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2">
+        <v>6</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="1"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>2</v>
+      </c>
+      <c r="B7" s="2">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="5">
-        <v>44989.791666666664</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2" s="4">
+      <c r="D7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H7" s="1"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>2</v>
+      </c>
+      <c r="B8" s="2">
+        <v>8</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4">
-        <v>2</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="D8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="1"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
         <v>3</v>
       </c>
-      <c r="E2" s="5">
-        <v>44989.770833333336</v>
-      </c>
-      <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" s="4">
+      <c r="B9" s="2">
+        <v>9</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" s="1"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>3</v>
+      </c>
+      <c r="B10" s="2">
+        <v>10</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="4">
-        <v>3</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="5">
-        <v>44989.8125</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4" s="4">
-        <v>2</v>
-      </c>
-      <c r="B4" s="4">
-        <v>4</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="5">
-        <v>44996.770833333336</v>
-      </c>
-      <c r="H4" s="1"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A5" s="4">
-        <v>2</v>
-      </c>
-      <c r="B5" s="4">
-        <v>5</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" s="6">
-        <v>44995.833333333336</v>
-      </c>
-      <c r="H5" s="1"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A6" s="4">
-        <v>2</v>
-      </c>
-      <c r="B6" s="4">
-        <v>6</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="6">
-        <v>44995.833333333336</v>
-      </c>
-      <c r="H6" s="1"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A7" s="4">
-        <v>3</v>
-      </c>
-      <c r="B7" s="4">
-        <v>7</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E7" s="7">
-        <v>45010.8125</v>
-      </c>
-      <c r="H7" s="1"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A8" s="4">
-        <v>3</v>
-      </c>
-      <c r="B8" s="4">
+      <c r="D10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E8" s="7">
-        <v>45010.791666666664</v>
-      </c>
-      <c r="H8" s="1"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A9" s="4">
-        <v>3</v>
-      </c>
-      <c r="B9" s="4">
-        <v>9</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="7">
-        <v>45010.770833333336</v>
-      </c>
-      <c r="H9" s="1"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A10" s="4">
-        <v>4</v>
-      </c>
-      <c r="B10" s="4">
-        <v>10</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E10" s="7">
-        <v>45030.833333333336</v>
+      <c r="E10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -645,20 +730,23 @@
       <c r="N10" s="1"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A11" s="4">
-        <v>4</v>
-      </c>
-      <c r="B11" s="4">
+      <c r="A11" s="2">
+        <v>3</v>
+      </c>
+      <c r="B11" s="2">
         <v>11</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E11" s="7">
-        <v>45030.833333333336</v>
+      <c r="C11" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -668,20 +756,23 @@
       <c r="N11" s="1"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A12" s="4">
+      <c r="A12" s="2">
+        <v>3</v>
+      </c>
+      <c r="B12" s="2">
+        <v>12</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="4">
-        <v>12</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E12" s="7">
-        <v>45031.770833333336</v>
+      <c r="E12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -691,20 +782,23 @@
       <c r="N12" s="1"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A13" s="4">
-        <v>5</v>
-      </c>
-      <c r="B13" s="4">
+      <c r="A13" s="2">
+        <v>4</v>
+      </c>
+      <c r="B13" s="2">
         <v>13</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E13" s="7">
-        <v>45037.833333333336</v>
+      <c r="C13" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>2</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -714,20 +808,23 @@
       <c r="N13" s="1"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14" s="4">
+      <c r="A14" s="2">
+        <v>4</v>
+      </c>
+      <c r="B14" s="2">
+        <v>14</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="B14" s="4">
-        <v>14</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E14" s="7">
-        <v>45038.8125</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -737,20 +834,23 @@
       <c r="N14" s="1"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A15" s="4">
-        <v>5</v>
-      </c>
-      <c r="B15" s="4">
+      <c r="A15" s="2">
+        <v>4</v>
+      </c>
+      <c r="B15" s="2">
         <v>15</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15" s="7">
-        <v>45038.770833333336</v>
+      <c r="C15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -760,20 +860,23 @@
       <c r="N15" s="1"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A16" s="4">
-        <v>6</v>
-      </c>
-      <c r="B16" s="4">
+      <c r="A16" s="2">
+        <v>4</v>
+      </c>
+      <c r="B16" s="2">
         <v>16</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E16" s="7">
-        <v>45044.833333333336</v>
+      <c r="E16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -783,20 +886,23 @@
       <c r="N16" s="1"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A17" s="4">
-        <v>6</v>
-      </c>
-      <c r="B17" s="4">
+      <c r="A17" s="2">
+        <v>5</v>
+      </c>
+      <c r="B17" s="2">
         <v>17</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E17" s="7">
-        <v>45045.770833333336</v>
+      <c r="C17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -806,20 +912,23 @@
       <c r="N17" s="1"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A18" s="4">
-        <v>6</v>
-      </c>
-      <c r="B18" s="4">
+      <c r="A18" s="2">
+        <v>5</v>
+      </c>
+      <c r="B18" s="2">
         <v>18</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E18" s="7">
-        <v>45045.8125</v>
+      <c r="C18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -829,20 +938,23 @@
       <c r="N18" s="1"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A19" s="4">
-        <v>7</v>
-      </c>
-      <c r="B19" s="4">
+      <c r="A19" s="2">
+        <v>5</v>
+      </c>
+      <c r="B19" s="2">
         <v>19</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E19" s="7">
-        <v>45058.833333333336</v>
+      <c r="C19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -852,20 +964,23 @@
       <c r="N19" s="1"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A20" s="4">
+      <c r="A20" s="2">
+        <v>5</v>
+      </c>
+      <c r="B20" s="2">
+        <v>20</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B20" s="4">
-        <v>20</v>
-      </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E20" s="7">
-        <v>45059.770833333336</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -875,20 +990,23 @@
       <c r="N20" s="1"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A21" s="4">
-        <v>7</v>
-      </c>
-      <c r="B21" s="4">
+      <c r="A21" s="2">
+        <v>6</v>
+      </c>
+      <c r="B21" s="2">
         <v>21</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E21" s="7">
-        <v>45058.833333333336</v>
+      <c r="C21" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -898,20 +1016,23 @@
       <c r="N21" s="1"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A22" s="4">
+      <c r="A22" s="2">
+        <v>6</v>
+      </c>
+      <c r="B22" s="2">
+        <v>22</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="4">
-        <v>22</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E22" s="8">
-        <v>45065.833333333336</v>
+      <c r="E22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -921,20 +1042,23 @@
       <c r="N22" s="1"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A23" s="4">
-        <v>8</v>
-      </c>
-      <c r="B23" s="4">
+      <c r="A23" s="2">
+        <v>6</v>
+      </c>
+      <c r="B23" s="2">
         <v>23</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E23" s="8">
-        <v>45066.770833333336</v>
+      <c r="C23" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -944,20 +1068,23 @@
       <c r="N23" s="1"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A24" s="4">
-        <v>8</v>
-      </c>
-      <c r="B24" s="4">
+      <c r="A24" s="2">
+        <v>6</v>
+      </c>
+      <c r="B24" s="2">
         <v>24</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E24" s="8">
-        <v>45065.833333333336</v>
+      <c r="C24" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
@@ -967,20 +1094,23 @@
       <c r="N24" s="1"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A25" s="4">
-        <v>9</v>
-      </c>
-      <c r="B25" s="4">
+      <c r="A25" s="2">
+        <v>7</v>
+      </c>
+      <c r="B25" s="2">
         <v>25</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E25" s="8">
-        <v>45073.791666666664</v>
+      <c r="C25" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
@@ -990,20 +1120,23 @@
       <c r="N25" s="1"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A26" s="4">
-        <v>9</v>
-      </c>
-      <c r="B26" s="4">
+      <c r="A26" s="2">
+        <v>7</v>
+      </c>
+      <c r="B26" s="2">
         <v>26</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E26" s="8">
-        <v>45073.770833333336</v>
       </c>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
@@ -1013,20 +1146,23 @@
       <c r="N26" s="1"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A27" s="4">
-        <v>9</v>
-      </c>
-      <c r="B27" s="4">
+      <c r="A27" s="2">
+        <v>7</v>
+      </c>
+      <c r="B27" s="2">
         <v>27</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E27" s="8">
-        <v>45072.833333333336</v>
+      <c r="E27" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
@@ -1036,20 +1172,23 @@
       <c r="N27" s="1"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A28" s="4">
-        <v>10</v>
-      </c>
-      <c r="B28" s="4">
+      <c r="A28" s="2">
+        <v>7</v>
+      </c>
+      <c r="B28" s="2">
         <v>28</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D28" s="3" t="s">
+      <c r="C28" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>2</v>
-      </c>
-      <c r="E28" s="8">
-        <v>45086.833333333336</v>
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
@@ -1060,20 +1199,23 @@
       <c r="N28" s="1"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A29" s="4">
+      <c r="A29" s="2">
+        <v>8</v>
+      </c>
+      <c r="B29" s="2">
+        <v>29</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B29" s="4">
-        <v>29</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E29" s="8">
-        <v>45086.833333333336</v>
+      <c r="D29" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
@@ -1084,20 +1226,23 @@
       <c r="N29" s="1"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A30" s="4">
-        <v>10</v>
-      </c>
-      <c r="B30" s="4">
+      <c r="A30" s="2">
+        <v>8</v>
+      </c>
+      <c r="B30" s="2">
         <v>30</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E30" s="8">
-        <v>45086.833333333336</v>
+      <c r="C30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
@@ -1108,20 +1253,23 @@
       <c r="N30" s="1"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A31" s="4">
-        <v>11</v>
-      </c>
-      <c r="B31" s="4">
+      <c r="A31" s="2">
+        <v>8</v>
+      </c>
+      <c r="B31" s="2">
         <v>31</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="D31" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E31" s="8">
-        <v>45093.833333333336</v>
+      <c r="E31" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -1131,20 +1279,23 @@
       <c r="N31" s="1"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A32" s="4">
-        <v>11</v>
-      </c>
-      <c r="B32" s="4">
+      <c r="A32" s="2">
+        <v>8</v>
+      </c>
+      <c r="B32" s="2">
         <v>32</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D32" s="3" t="s">
+      <c r="C32" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E32" s="8">
-        <v>45094.770833333336</v>
+      <c r="D32" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -1154,20 +1305,23 @@
       <c r="N32" s="1"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A33" s="4">
+      <c r="A33" s="2">
+        <v>9</v>
+      </c>
+      <c r="B33" s="2">
+        <v>33</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F33" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="B33" s="4">
-        <v>33</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E33" s="8">
-        <v>45094.8125</v>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -1177,20 +1331,23 @@
       <c r="N33" s="1"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A34" s="4">
-        <v>12</v>
-      </c>
-      <c r="B34" s="4">
+      <c r="A34" s="2">
+        <v>9</v>
+      </c>
+      <c r="B34" s="2">
         <v>34</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E34" s="8">
-        <v>45101.770833333336</v>
+      <c r="C34" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -1200,20 +1357,23 @@
       <c r="N34" s="1"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A35" s="4">
-        <v>12</v>
-      </c>
-      <c r="B35" s="4">
+      <c r="A35" s="2">
+        <v>9</v>
+      </c>
+      <c r="B35" s="2">
         <v>35</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D35" s="3" t="s">
+      <c r="C35" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F35" s="2" t="s">
         <v>2</v>
-      </c>
-      <c r="E35" s="8">
-        <v>45100.833333333336</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
@@ -1223,20 +1383,23 @@
       <c r="N35" s="1"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A36" s="4">
-        <v>12</v>
-      </c>
-      <c r="B36" s="4">
+      <c r="A36" s="2">
+        <v>9</v>
+      </c>
+      <c r="B36" s="2">
         <v>36</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E36" s="8">
-        <v>45101.791666666664</v>
+      <c r="C36" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -1246,20 +1409,23 @@
       <c r="N36" s="1"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A37" s="4">
-        <v>13</v>
-      </c>
-      <c r="B37" s="4">
+      <c r="A37" s="2">
+        <v>10</v>
+      </c>
+      <c r="B37" s="2">
         <v>37</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E37" s="8">
-        <v>45114.833333333336</v>
+      <c r="C37" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
@@ -1269,20 +1435,23 @@
       <c r="N37" s="1"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A38" s="4">
-        <v>13</v>
-      </c>
-      <c r="B38" s="4">
+      <c r="A38" s="2">
+        <v>10</v>
+      </c>
+      <c r="B38" s="2">
         <v>38</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E38" s="8">
-        <v>45114.833333333336</v>
+      <c r="C38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
@@ -1292,20 +1461,23 @@
       <c r="N38" s="1"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A39" s="4">
-        <v>13</v>
-      </c>
-      <c r="B39" s="4">
+      <c r="A39" s="2">
+        <v>10</v>
+      </c>
+      <c r="B39" s="2">
         <v>39</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E39" s="8">
-        <v>45115.8125</v>
+      <c r="C39" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
@@ -1315,20 +1487,23 @@
       <c r="N39" s="1"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A40" s="4">
-        <v>14</v>
-      </c>
-      <c r="B40" s="4">
+      <c r="A40" s="2">
+        <v>10</v>
+      </c>
+      <c r="B40" s="2">
         <v>40</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E40" s="8">
-        <v>45122.770833333336</v>
+      <c r="C40" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>2</v>
       </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
@@ -1338,20 +1513,23 @@
       <c r="N40" s="1"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A41" s="4">
-        <v>14</v>
-      </c>
-      <c r="B41" s="4">
+      <c r="A41" s="2">
+        <v>11</v>
+      </c>
+      <c r="B41" s="2">
         <v>41</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E41" s="8">
-        <v>45122.8125</v>
+      <c r="C41" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
@@ -1361,20 +1539,23 @@
       <c r="N41" s="1"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A42" s="4">
-        <v>14</v>
-      </c>
-      <c r="B42" s="4">
+      <c r="A42" s="2">
+        <v>11</v>
+      </c>
+      <c r="B42" s="2">
         <v>42</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E42" s="8">
-        <v>45122.791666666664</v>
+      <c r="C42" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
@@ -1383,6 +1564,286 @@
       <c r="L42" s="1"/>
       <c r="N42" s="1"/>
     </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A43" s="2">
+        <v>11</v>
+      </c>
+      <c r="B43" s="2">
+        <v>43</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A44" s="2">
+        <v>11</v>
+      </c>
+      <c r="B44" s="2">
+        <v>44</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A45" s="2">
+        <v>12</v>
+      </c>
+      <c r="B45" s="2">
+        <v>45</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A46" s="2">
+        <v>12</v>
+      </c>
+      <c r="B46" s="2">
+        <v>46</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A47" s="2">
+        <v>12</v>
+      </c>
+      <c r="B47" s="2">
+        <v>47</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A48" s="2">
+        <v>12</v>
+      </c>
+      <c r="B48" s="2">
+        <v>48</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A49" s="2">
+        <v>13</v>
+      </c>
+      <c r="B49" s="2">
+        <v>49</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A50" s="2">
+        <v>13</v>
+      </c>
+      <c r="B50" s="2">
+        <v>50</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A51" s="2">
+        <v>13</v>
+      </c>
+      <c r="B51" s="2">
+        <v>51</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A52" s="2">
+        <v>13</v>
+      </c>
+      <c r="B52" s="2">
+        <v>52</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A53" s="2">
+        <v>14</v>
+      </c>
+      <c r="B53" s="2">
+        <v>53</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A54" s="2">
+        <v>14</v>
+      </c>
+      <c r="B54" s="2">
+        <v>54</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A55" s="2">
+        <v>14</v>
+      </c>
+      <c r="B55" s="2">
+        <v>55</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A56" s="2">
+        <v>14</v>
+      </c>
+      <c r="B56" s="2">
+        <v>56</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
